--- a/artfynd/A 34414-2024 artfynd.xlsx
+++ b/artfynd/A 34414-2024 artfynd.xlsx
@@ -3048,10 +3048,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119528530</v>
+        <v>119528467</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>90582</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581949</v>
+        <v>581999</v>
       </c>
       <c r="R23" t="n">
-        <v>6425863</v>
+        <v>6425876</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119528467</v>
+        <v>119528530</v>
       </c>
       <c r="B24" t="n">
-        <v>90582</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3178,21 +3178,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581999</v>
+        <v>581949</v>
       </c>
       <c r="R24" t="n">
-        <v>6425876</v>
+        <v>6425863</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 34414-2024 artfynd.xlsx
+++ b/artfynd/A 34414-2024 artfynd.xlsx
@@ -3048,10 +3048,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119528467</v>
+        <v>119528530</v>
       </c>
       <c r="B23" t="n">
-        <v>90582</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581999</v>
+        <v>581949</v>
       </c>
       <c r="R23" t="n">
-        <v>6425876</v>
+        <v>6425863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119528530</v>
+        <v>119528467</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>90582</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3178,21 +3178,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581949</v>
+        <v>581999</v>
       </c>
       <c r="R24" t="n">
-        <v>6425863</v>
+        <v>6425876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 34414-2024 artfynd.xlsx
+++ b/artfynd/A 34414-2024 artfynd.xlsx
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119528510</v>
+        <v>119528547</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,25 +2272,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581950</v>
+        <v>581954</v>
       </c>
       <c r="R16" t="n">
-        <v>6425860</v>
+        <v>6425856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119528496</v>
+        <v>119528510</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,35 +2386,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581964</v>
+        <v>581950</v>
       </c>
       <c r="R17" t="n">
-        <v>6425859</v>
+        <v>6425860</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119528681</v>
+        <v>119528478</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2614,35 +2614,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2650,10 +2653,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582061</v>
+        <v>581966</v>
       </c>
       <c r="R19" t="n">
-        <v>6425819</v>
+        <v>6425859</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119528640</v>
+        <v>119528595</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,34 +2732,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2764,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582019</v>
+        <v>581931</v>
       </c>
       <c r="R20" t="n">
-        <v>6425824</v>
+        <v>6425869</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119528595</v>
+        <v>119528613</v>
       </c>
       <c r="B21" t="n">
-        <v>94681</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,27 +2839,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2871,10 +2874,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581931</v>
+        <v>581990</v>
       </c>
       <c r="R21" t="n">
-        <v>6425869</v>
+        <v>6425841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2934,10 +2937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119528478</v>
+        <v>119528467</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,25 +2949,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2985,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581966</v>
+        <v>581999</v>
       </c>
       <c r="R22" t="n">
-        <v>6425859</v>
+        <v>6425876</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119528530</v>
+        <v>119528681</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,38 +3063,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581949</v>
+        <v>582061</v>
       </c>
       <c r="R23" t="n">
-        <v>6425863</v>
+        <v>6425819</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,10 +3162,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119528467</v>
+        <v>119528628</v>
       </c>
       <c r="B24" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,25 +3174,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581999</v>
+        <v>582001</v>
       </c>
       <c r="R24" t="n">
-        <v>6425876</v>
+        <v>6425841</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119528662</v>
+        <v>119528640</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3288,25 +3288,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3314,13 +3314,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3334,7 +3333,7 @@
         <v>6425824</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3372,6 +3371,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119528628</v>
+        <v>119528496</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3402,35 +3402,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582001</v>
+        <v>581964</v>
       </c>
       <c r="R26" t="n">
-        <v>6425841</v>
+        <v>6425859</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119528547</v>
+        <v>119528530</v>
       </c>
       <c r="B27" t="n">
         <v>91832</v>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581954</v>
+        <v>581949</v>
       </c>
       <c r="R27" t="n">
-        <v>6425856</v>
+        <v>6425863</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119528613</v>
+        <v>119528662</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3630,25 +3630,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3656,12 +3656,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3669,13 +3670,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581990</v>
+        <v>582019</v>
       </c>
       <c r="R28" t="n">
-        <v>6425841</v>
+        <v>6425824</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3713,7 +3714,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34414-2024 artfynd.xlsx
+++ b/artfynd/A 34414-2024 artfynd.xlsx
@@ -3051,10 +3051,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119528681</v>
+        <v>119528628</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,35 +3063,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3099,10 +3102,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582061</v>
+        <v>582001</v>
       </c>
       <c r="R23" t="n">
-        <v>6425819</v>
+        <v>6425841</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119528628</v>
+        <v>119528681</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,38 +3177,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582001</v>
+        <v>582061</v>
       </c>
       <c r="R24" t="n">
-        <v>6425841</v>
+        <v>6425819</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 34414-2024 artfynd.xlsx
+++ b/artfynd/A 34414-2024 artfynd.xlsx
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">

--- a/artfynd/A 34414-2024 artfynd.xlsx
+++ b/artfynd/A 34414-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119341034</v>
+        <v>119341107</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581812</v>
+        <v>581699</v>
       </c>
       <c r="R2" t="n">
-        <v>6425957</v>
+        <v>6426110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I granplantering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119340763</v>
+        <v>119341034</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +800,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581872</v>
+        <v>581812</v>
       </c>
       <c r="R3" t="n">
-        <v>6426091</v>
+        <v>6425957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -896,45 +891,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119340896</v>
+        <v>119528595</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581763</v>
+        <v>581931</v>
       </c>
       <c r="R4" t="n">
-        <v>6425945</v>
+        <v>6425869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,47 +993,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119340856</v>
+        <v>119461474</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581787</v>
+        <v>581959</v>
       </c>
       <c r="R5" t="n">
-        <v>6425974</v>
+        <v>6425857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,12 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,37 +1102,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119341107</v>
+        <v>119461505</v>
       </c>
       <c r="B6" t="n">
-        <v>91182</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,7 +1137,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1169,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581699</v>
+        <v>581948</v>
       </c>
       <c r="R6" t="n">
-        <v>6426110</v>
+        <v>6425862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,17 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I granplantering</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,37 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119341080</v>
+        <v>119528530</v>
       </c>
       <c r="B7" t="n">
-        <v>91836</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581744</v>
+        <v>581949</v>
       </c>
       <c r="R7" t="n">
-        <v>6425980</v>
+        <v>6425863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1287,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1351,47 +1320,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119340841</v>
+        <v>119528547</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1399,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581756</v>
+        <v>581954</v>
       </c>
       <c r="R8" t="n">
-        <v>6425982</v>
+        <v>6425856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,12 +1396,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,37 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119340797</v>
+        <v>119528560</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1513,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581866</v>
+        <v>581951</v>
       </c>
       <c r="R9" t="n">
-        <v>6426052</v>
+        <v>6425856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,19 +1505,19 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1576,15 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119461547</v>
+        <v>119341080</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1616,7 +1573,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1627,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582021</v>
+        <v>581744</v>
       </c>
       <c r="R10" t="n">
-        <v>6425805</v>
+        <v>6425980</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,19 +1614,19 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
@@ -1690,19 +1647,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119461615</v>
+        <v>119340763</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1725,12 +1677,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1741,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581968</v>
+        <v>581872</v>
       </c>
       <c r="R11" t="n">
-        <v>6425850</v>
+        <v>6426091</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,19 +1723,19 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
@@ -1804,15 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119461474</v>
+        <v>119340797</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,31 +1767,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1855,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581959</v>
+        <v>581866</v>
       </c>
       <c r="R12" t="n">
-        <v>6425857</v>
+        <v>6426052</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,19 +1832,19 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
@@ -1918,15 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119461505</v>
+        <v>119461525</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,26 +1876,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1969,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581948</v>
+        <v>581985</v>
       </c>
       <c r="R13" t="n">
-        <v>6425862</v>
+        <v>6425840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,19 +1974,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119461525</v>
+        <v>119461547</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2067,7 +2004,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2083,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581985</v>
+        <v>582021</v>
       </c>
       <c r="R14" t="n">
-        <v>6425840</v>
+        <v>6425805</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,15 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119461456</v>
+        <v>119461615</v>
       </c>
       <c r="B15" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,26 +2094,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2197,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581964</v>
+        <v>581968</v>
       </c>
       <c r="R15" t="n">
-        <v>6425855</v>
+        <v>6425850</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2260,15 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119528547</v>
+        <v>119528478</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2311,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581954</v>
+        <v>581966</v>
       </c>
       <c r="R16" t="n">
-        <v>6425856</v>
+        <v>6425859</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,16 +2304,11 @@
         <v>119528510</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2488,15 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119528560</v>
+        <v>119528613</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2539,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581951</v>
+        <v>581990</v>
       </c>
       <c r="R18" t="n">
-        <v>6425856</v>
+        <v>6425841</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,19 +2519,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119528478</v>
+        <v>119528628</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2653,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581966</v>
+        <v>582001</v>
       </c>
       <c r="R19" t="n">
-        <v>6425859</v>
+        <v>6425841</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,43 +2628,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119528595</v>
+        <v>119528640</v>
       </c>
       <c r="B20" t="n">
-        <v>94681</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2760,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581931</v>
+        <v>582019</v>
       </c>
       <c r="R20" t="n">
-        <v>6425869</v>
+        <v>6425824</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,37 +2737,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119528613</v>
+        <v>119528467</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2874,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581990</v>
+        <v>581999</v>
       </c>
       <c r="R21" t="n">
-        <v>6425841</v>
+        <v>6425876</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,15 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119528467</v>
+        <v>119528573</v>
       </c>
       <c r="B22" t="n">
-        <v>90582</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2977,7 +2881,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2988,10 +2892,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581999</v>
+        <v>581882</v>
       </c>
       <c r="R22" t="n">
-        <v>6425876</v>
+        <v>6425872</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,15 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119528628</v>
+        <v>119528811</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,21 +2966,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3091,7 +2990,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3102,13 +3001,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582001</v>
+        <v>582040</v>
       </c>
       <c r="R23" t="n">
-        <v>6425841</v>
+        <v>6425918</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3165,61 +3064,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119528681</v>
+        <v>88952616</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 34414, Ryven, Sm</t>
+          <t>Ryven/Solberga, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582061</v>
+        <v>581904</v>
       </c>
       <c r="R24" t="n">
-        <v>6425819</v>
+        <v>6425912</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3243,12 +3140,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,56 +3164,50 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Martin Rosenblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Martin Rosenblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119528640</v>
+        <v>119341056</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3314,12 +3215,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3327,13 +3229,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582019</v>
+        <v>581833</v>
       </c>
       <c r="R25" t="n">
-        <v>6425824</v>
+        <v>6425965</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3357,12 +3259,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3273,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3390,15 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119528496</v>
+        <v>119528662</v>
       </c>
       <c r="B26" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,34 +3302,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3441,13 +3338,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581964</v>
+        <v>582019</v>
       </c>
       <c r="R26" t="n">
-        <v>6425859</v>
+        <v>6425824</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3485,7 +3382,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3504,50 +3400,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119528530</v>
+        <v>119340841</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3555,10 +3443,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581949</v>
+        <v>581756</v>
       </c>
       <c r="R27" t="n">
-        <v>6425863</v>
+        <v>6425982</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3585,12 +3473,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,51 +3506,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119528662</v>
+        <v>119340856</v>
       </c>
       <c r="B28" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3670,13 +3549,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582019</v>
+        <v>581787</v>
       </c>
       <c r="R28" t="n">
-        <v>6425824</v>
+        <v>6425974</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3700,12 +3579,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,6 +3593,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3729,6 +3609,430 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>119340896</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 34414, Ryven, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>581763</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6425945</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>119341019</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 34414, Ryven, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>581827</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6425967</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119528681</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 34414, Ryven, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>582061</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6425819</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>119528696</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 34414, Ryven, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>582063</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6425827</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
